--- a/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,71</t>
+          <t>0,54; 5,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,4; 19,58</t>
+          <t>9,69; 19,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,12; 10,66</t>
+          <t>2,76; 10,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,14</t>
+          <t>2,32; 8,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,07; 25,4</t>
+          <t>14,06; 25,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 21,61</t>
+          <t>2,98; 21,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,09; 6,25</t>
+          <t>2,01; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,26; 20,95</t>
+          <t>13,55; 20,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,91; 14,29</t>
+          <t>3,75; 15,71</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,57</t>
+          <t>1,81; 6,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,83; 17,13</t>
+          <t>9,55; 16,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 24,57</t>
+          <t>10,16; 24,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 5,05</t>
+          <t>1,25; 4,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,71; 18,79</t>
+          <t>10,98; 18,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 14,75</t>
+          <t>7,5; 14,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,38</t>
+          <t>1,9; 4,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 16,34</t>
+          <t>11,25; 16,48</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,4; 16,9</t>
+          <t>9,52; 17,22</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 10,84</t>
+          <t>4,11; 10,42</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,82; 20,88</t>
+          <t>11,83; 20,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,14; 27,71</t>
+          <t>12,77; 28,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,93; 8,91</t>
+          <t>2,92; 8,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,82; 26,82</t>
+          <t>16,43; 26,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,07; 31,81</t>
+          <t>19,09; 32,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,1; 8,34</t>
+          <t>4,25; 8,52</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,5; 22,36</t>
+          <t>15,33; 22,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,71; 27,92</t>
+          <t>17,02; 27,96</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,53</t>
+          <t>2,05; 7,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,99; 13,81</t>
+          <t>7,19; 14,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,72; 13,22</t>
+          <t>5,69; 12,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 7,16</t>
+          <t>2,03; 7,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,8; 11,31</t>
+          <t>4,83; 11,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 16,88</t>
+          <t>7,03; 17,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 6,07</t>
+          <t>2,38; 6,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,59</t>
+          <t>6,76; 11,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,4; 13,42</t>
+          <t>7,54; 13,48</t>
         </is>
       </c>
     </row>
@@ -1120,42 +1123,42 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,14; 15,27</t>
+          <t>11,16; 15,42</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,82; 16,72</t>
+          <t>10,97; 16,66</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,96; 5,5</t>
+          <t>2,97; 5,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,81; 17,53</t>
+          <t>12,95; 17,72</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,4; 16,98</t>
+          <t>11,33; 17,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,0</t>
+          <t>3,28; 5,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,53; 15,66</t>
+          <t>12,66; 15,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,98; 16,04</t>
+          <t>11,79; 16,12</t>
         </is>
       </c>
     </row>
@@ -1180,4 +1183,955 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19044</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6686</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28285</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>11451</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>10553</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>47329</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>18137</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>745; 7652</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>12877; 25883</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3232; 12188</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3594; 13031</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20820; 37482</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>4180; 30558</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>5898; 17665</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>38060; 58302</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9665; 40489</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>6841</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26517</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>27945</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>32210</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>27326</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12792</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>58726</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>55271</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>3721; 12432</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>19665; 34853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>19254; 45815</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2798; 10979</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>24564; 41973</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19079; 37794</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>8133; 19773</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>48328; 70799</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>42239; 76427</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>10497</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>25256</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>40180</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>35518</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>46270</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>19255</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>60774</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>86450</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>6385; 16188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>18459; 32350</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>24322; 53665</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4820; 14466</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>27255; 44317</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>35369; 60262</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>13637; 27317</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>49349; 71879</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>63936; 105024</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>8476</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21168</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>14883</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>15251</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20507</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16859</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>36419</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>35390</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>4286; 16052</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>14766; 29637</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>9554; 21315</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>4221; 15196</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>9781; 22494</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12666; 30991</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>9929; 25265</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>27560; 46857</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>26249; 46929</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>28922</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>91985</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>89694</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>105554</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>59459</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>203248</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>195248</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>21329; 39146</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>78140; 107958</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>72945; 110824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>22306; 41019</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>95798; 131128</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>86163; 130400</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>47894; 74764</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>182313; 228599</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>168093; 229820</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,53</t>
+          <t>0,55; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,69; 19,48</t>
+          <t>9,52; 19,58</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,76; 10,39</t>
+          <t>3,01; 10,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 8,42</t>
+          <t>2,44; 9,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>14,06; 25,31</t>
+          <t>13,72; 25,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 21,76</t>
+          <t>2,92; 22,79</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 6,03</t>
+          <t>2,12; 5,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,55; 20,75</t>
+          <t>13,09; 21,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,75; 15,71</t>
+          <t>3,95; 14,49</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,81; 6,06</t>
+          <t>1,82; 5,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,55; 16,92</t>
+          <t>9,45; 16,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,16; 24,17</t>
+          <t>10,01; 24,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,9</t>
+          <t>1,31; 5,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,98; 18,76</t>
+          <t>10,92; 18,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,86</t>
+          <t>7,51; 14,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 4,61</t>
+          <t>1,89; 4,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,25; 16,48</t>
+          <t>10,97; 16,51</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 17,22</t>
+          <t>9,58; 17,46</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4,11; 10,42</t>
+          <t>3,89; 10,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,83; 20,74</t>
+          <t>12,04; 20,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12,77; 28,19</t>
+          <t>13,05; 28,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 8,75</t>
+          <t>2,85; 8,71</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,43; 26,71</t>
+          <t>16,32; 26,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,09; 32,52</t>
+          <t>18,8; 32,45</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,25; 8,52</t>
+          <t>4,01; 8,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,33; 22,33</t>
+          <t>15,56; 22,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,02; 27,96</t>
+          <t>17,36; 28,16</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,05; 7,66</t>
+          <t>2,06; 7,06</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 14,43</t>
+          <t>7,35; 13,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 12,69</t>
+          <t>5,82; 12,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,29</t>
+          <t>2,1; 7,41</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,83; 11,12</t>
+          <t>4,84; 10,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,03; 17,19</t>
+          <t>7,35; 17,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,38; 6,05</t>
+          <t>2,57; 6,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,76; 11,49</t>
+          <t>6,54; 11,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,54; 13,48</t>
+          <t>7,66; 13,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,53</t>
+          <t>2,93; 5,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,16; 15,42</t>
+          <t>11,36; 15,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,66</t>
+          <t>10,8; 16,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,45</t>
+          <t>2,95; 5,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,95; 17,72</t>
+          <t>12,99; 17,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,33; 17,15</t>
+          <t>11,3; 16,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,28; 5,12</t>
+          <t>3,22; 4,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,66; 15,87</t>
+          <t>12,6; 15,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,79; 16,12</t>
+          <t>11,83; 16,04</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>745; 7652</t>
+          <t>766; 7670</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12877; 25883</t>
+          <t>12651; 26021</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3232; 12188</t>
+          <t>3527; 12609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3594; 13031</t>
+          <t>3770; 14164</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20820; 37482</t>
+          <t>20311; 37688</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4180; 30558</t>
+          <t>4102; 31995</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5898; 17665</t>
+          <t>6207; 17562</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>38060; 58302</t>
+          <t>36780; 59108</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9665; 40489</t>
+          <t>10169; 37349</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3721; 12432</t>
+          <t>3731; 12073</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19665; 34853</t>
+          <t>19457; 34837</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>19254; 45815</t>
+          <t>18973; 47111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2798; 10979</t>
+          <t>2931; 11197</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24564; 41973</t>
+          <t>24423; 41614</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19079; 37794</t>
+          <t>19098; 36604</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8133; 19773</t>
+          <t>8123; 18941</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48328; 70799</t>
+          <t>47121; 70939</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42239; 76427</t>
+          <t>42542; 77487</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6385; 16188</t>
+          <t>6042; 15665</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18459; 32350</t>
+          <t>18782; 31910</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24322; 53665</t>
+          <t>24856; 54483</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4820; 14466</t>
+          <t>4705; 14402</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27255; 44317</t>
+          <t>27078; 44092</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35369; 60262</t>
+          <t>34842; 60133</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13637; 27317</t>
+          <t>12856; 27039</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>49349; 71879</t>
+          <t>50099; 72914</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>63936; 105024</t>
+          <t>65203; 105776</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4286; 16052</t>
+          <t>4317; 14787</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14766; 29637</t>
+          <t>15084; 28652</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9554; 21315</t>
+          <t>9767; 20953</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4221; 15196</t>
+          <t>4378; 15440</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9781; 22494</t>
+          <t>9788; 21579</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12666; 30991</t>
+          <t>13255; 31914</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9929; 25265</t>
+          <t>10738; 26151</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>27560; 46857</t>
+          <t>26672; 46468</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26249; 46929</t>
+          <t>26690; 47146</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21329; 39146</t>
+          <t>20748; 37967</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78140; 107958</t>
+          <t>79563; 105936</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>72945; 110824</t>
+          <t>71831; 111837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22306; 41019</t>
+          <t>22184; 42082</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>95798; 131128</t>
+          <t>96101; 128502</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>86163; 130400</t>
+          <t>85913; 128326</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47894; 74764</t>
+          <t>47059; 72732</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>182313; 228599</t>
+          <t>181435; 227202</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>168093; 229820</t>
+          <t>168616; 228630</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$notiene-Habitat-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>4,81%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>19,1%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>4,85%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>2,25%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>14,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>5,7%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4,81%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>19,1%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 5,54</t>
+          <t>2,31; 9,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 19,58</t>
+          <t>14,07; 25,4</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,01; 10,75</t>
+          <t>2,28; 8,81</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,44; 9,16</t>
+          <t>0,54; 5,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>13,72; 25,45</t>
+          <t>9,4; 19,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,92; 22,79</t>
+          <t>3,02; 10,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,12; 5,99</t>
+          <t>2,09; 6,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>13,09; 21,04</t>
+          <t>13,26; 20,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>3,95; 14,49</t>
+          <t>2,98; 7,9</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,66%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>14,4%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,08%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>3,34%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>12,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>14,75%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>10,58%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,89</t>
+          <t>1,15; 5,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,45; 16,91</t>
+          <t>10,71; 18,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 24,86</t>
+          <t>6,79; 13,9</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,31; 5,0</t>
+          <t>1,69; 5,57</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,92; 18,6</t>
+          <t>9,83; 17,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,51; 14,39</t>
+          <t>8,03; 16,09</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89; 4,42</t>
+          <t>1,81; 4,38</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,97; 16,51</t>
+          <t>11,19; 16,34</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,58; 17,46</t>
+          <t>8,31; 13,4</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5,3%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>21,41%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23,07%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6,76%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>16,19%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>21,1%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>21,41%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>22,48%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,89; 10,08</t>
+          <t>2,93; 8,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,04; 20,46</t>
+          <t>15,82; 26,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13,05; 28,61</t>
+          <t>17,73; 29,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,85; 8,71</t>
+          <t>4,18; 10,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,32; 26,58</t>
+          <t>11,82; 20,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>18,8; 32,45</t>
+          <t>16,8; 27,37</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,01; 8,43</t>
+          <t>4,1; 8,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>15,56; 22,65</t>
+          <t>15,5; 22,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>17,36; 28,16</t>
+          <t>18,46; 26,75</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7,54%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>4,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>10,31%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>8,86%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,54%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,09%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 7,06</t>
+          <t>1,96; 7,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 13,95</t>
+          <t>4,8; 11,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 12,47</t>
+          <t>7,33; 16,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,1; 7,41</t>
+          <t>1,92; 7,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,84; 10,67</t>
+          <t>6,99; 13,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,35; 17,7</t>
+          <t>5,7; 13,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 6,26</t>
+          <t>2,47; 6,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,54; 11,4</t>
+          <t>6,96; 11,59</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,66; 13,54</t>
+          <t>7,44; 13,26</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>15,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>12,53%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>13,14%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>13,48%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,37%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,93; 5,36</t>
+          <t>2,96; 5,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,36; 15,13</t>
+          <t>12,81; 17,53</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,8; 16,81</t>
+          <t>10,48; 15,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,95; 5,59</t>
+          <t>3,01; 5,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,99; 17,36</t>
+          <t>11,14; 15,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,3; 16,88</t>
+          <t>10,2; 14,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 4,98</t>
+          <t>3,28; 5,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>12,6; 15,78</t>
+          <t>12,53; 15,66</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,83; 16,04</t>
+          <t>10,79; 14,0</t>
         </is>
       </c>
     </row>
@@ -1210,20 +1210,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que no dispone de calefacción en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7446</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>28285</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6101</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>3107</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>19044</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>6686</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7446</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>28285</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11451</t>
+          <t>6706</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>12807</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>766; 7670</t>
+          <t>3577; 14142</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12651; 26021</t>
+          <t>20833; 37611</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3527; 12609</t>
+          <t>2866; 11094</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3770; 14164</t>
+          <t>752; 7898</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>20311; 37688</t>
+          <t>12495; 26013</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4102; 31995</t>
+          <t>3651; 12576</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6207; 17562</t>
+          <t>6113; 18310</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36780; 59108</t>
+          <t>37261; 58854</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10169; 37349</t>
+          <t>7369; 19522</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>33</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>5951</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32210</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>23842</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>6841</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>26517</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>5951</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>32210</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27326</t>
+          <t>20582</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>55271</t>
+          <t>44425</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3731; 12073</t>
+          <t>2564; 11299</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19457; 34837</t>
+          <t>23954; 42028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18973; 47111</t>
+          <t>16068; 32878</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2931; 11197</t>
+          <t>3467; 11426</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24423; 41614</t>
+          <t>20243; 35294</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19098; 36604</t>
+          <t>14729; 29506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8123; 18941</t>
+          <t>7770; 18797</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47121; 70939</t>
+          <t>48087; 70189</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42542; 77487</t>
+          <t>34915; 56260</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>51</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>8757</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>35518</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>38839</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>10497</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>25256</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>40180</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8757</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>35518</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46270</t>
+          <t>34320</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>86450</t>
+          <t>73159</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>6042; 15665</t>
+          <t>4839; 14729</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18782; 31910</t>
+          <t>26254; 44495</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>24856; 54483</t>
+          <t>29851; 48953</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4705; 14402</t>
+          <t>6496; 16840</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27078; 44092</t>
+          <t>18442; 32565</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34842; 60133</t>
+          <t>26385; 42983</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12856; 27039</t>
+          <t>13144; 26733</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>50099; 72914</t>
+          <t>49896; 71978</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>65203; 105776</t>
+          <t>60056; 87050</t>
         </is>
       </c>
     </row>
@@ -1805,27 +1805,27 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>23</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8383</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15251</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>18857</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>8476</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>21168</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>14883</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>8383</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15251</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>14992</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>35390</t>
+          <t>33849</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4317; 14787</t>
+          <t>4077; 14913</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15084; 28652</t>
+          <t>9716; 22887</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9767; 20953</t>
+          <t>12337; 27459</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4378; 15440</t>
+          <t>4017; 15785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9788; 21579</t>
+          <t>14359; 28349</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13255; 31914</t>
+          <t>9535; 22156</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10738; 26151</t>
+          <t>10340; 25365</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>26672; 46468</t>
+          <t>28389; 47238</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26690; 47146</t>
+          <t>24969; 44482</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>117</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>30537</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>111264</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>87640</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>28922</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>91985</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>89694</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>111264</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>105554</t>
+          <t>76600</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>195248</t>
+          <t>164240</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>20748; 37967</t>
+          <t>22281; 41389</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>79563; 105936</t>
+          <t>94773; 129732</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>71831; 111837</t>
+          <t>73275; 105461</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22184; 42082</t>
+          <t>21305; 39198</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>96101; 128502</t>
+          <t>78028; 106883</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85913; 128326</t>
+          <t>64089; 90782</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>47059; 72732</t>
+          <t>47920; 73045</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>181435; 227202</t>
+          <t>180428; 225587</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>168616; 228630</t>
+          <t>143231; 185929</t>
         </is>
       </c>
     </row>
